--- a/document/hybrid document.xlsx
+++ b/document/hybrid document.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Ubrs\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{330E2365-1DB4-4042-97D2-AAC4075C45F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6507758D-7F2B-4E29-ABB0-B5C7806FD9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E216A6B-0620-468F-A1C0-8BA02934A3B0}"/>
+    <workbookView xWindow="5265" yWindow="5265" windowWidth="15330" windowHeight="8955" xr2:uid="{6E216A6B-0620-468F-A1C0-8BA02934A3B0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Exam" sheetId="3" r:id="rId1"/>
-    <sheet name="Test" sheetId="2" r:id="rId2"/>
-    <sheet name="Student" sheetId="1" r:id="rId3"/>
+    <sheet name="Test" sheetId="2" r:id="rId1"/>
+    <sheet name="Student" sheetId="1" r:id="rId2"/>
+    <sheet name="Exam" sheetId="3" r:id="rId3"/>
     <sheet name="Student001" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -572,108 +572,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F61908-2330-4CC5-B187-DE85B22DADA9}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="4">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="4">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="4">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="4">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="4">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="4">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="4">
-        <v>68</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E59BD07D-0F8D-472D-80A1-3D904E2D445F}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -775,7 +673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A365D5FD-394B-4238-8854-C843CD9EC710}">
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1040,6 +938,108 @@
       </c>
       <c r="G11" s="3">
         <v>41065</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78F61908-2330-4CC5-B187-DE85B22DADA9}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="4">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
